--- a/Base de dados.xlsx
+++ b/Base de dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoisdra-my.sharepoint.com/personal/nathalia_silveira_fibraplac_com_br1/Documents/Base Controle de Rejeitos_/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_7F4755BF84DCCE43E268565A8931F45BFA75341E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52367E7E-8B48-4AC8-AB27-B2D4EAB191A6}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="11_7F4755BF84DCCE43E268565A8931F45BFA75341E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EFD7588-DC0C-47D1-B923-9CB66499A797}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="120">
   <si>
     <t>Linha</t>
   </si>
@@ -556,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -626,22 +626,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1079,13 +1068,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="medium">
           <color indexed="64"/>
         </top>
@@ -1119,6 +1101,13 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1170,8 +1159,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{18F31E58-98E3-4CD2-AAB2-8DC3884DC1E1}" name="Tabela2" displayName="Tabela2" ref="A1:J148" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" headerRowBorderDxfId="10" tableBorderDxfId="11">
-  <autoFilter ref="A1:J148" xr:uid="{18F31E58-98E3-4CD2-AAB2-8DC3884DC1E1}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{18F31E58-98E3-4CD2-AAB2-8DC3884DC1E1}" name="Tabela2" displayName="Tabela2" ref="A1:J149" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
+  <autoFilter ref="A1:J149" xr:uid="{18F31E58-98E3-4CD2-AAB2-8DC3884DC1E1}">
     <filterColumn colId="1">
       <filters>
         <dateGroupItem year="2026" month="9" day="22" dateTimeGrouping="day"/>
@@ -1513,7 +1502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="13" bestFit="1" customWidth="1"/>
@@ -4815,7 +4804,7 @@
         <v>11</v>
       </c>
       <c r="D101" s="5">
-        <f t="shared" ref="D101:D148" si="2">((E101*F101*2750)/1000000000)*G101</f>
+        <f t="shared" ref="D101:D149" si="2">((E101*F101*2750)/1000000000)*G101</f>
         <v>0.24236410000000003</v>
       </c>
       <c r="E101" s="7">
@@ -5988,32 +5977,32 @@
       <c r="A137" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B137" s="23">
+      <c r="B137" s="8">
         <v>46287</v>
       </c>
-      <c r="C137" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D137" s="25">
+      <c r="C137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D137" s="5">
         <f t="shared" si="2"/>
         <v>2.1812769000000003</v>
       </c>
-      <c r="E137" s="26">
-        <v>15.8</v>
-      </c>
-      <c r="F137" s="24">
-        <v>5578</v>
-      </c>
-      <c r="G137" s="26">
+      <c r="E137" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="F137" s="4">
+        <v>5578</v>
+      </c>
+      <c r="G137" s="7">
         <v>9</v>
       </c>
-      <c r="H137" s="26" t="s">
+      <c r="H137" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I137" s="26" t="s">
+      <c r="I137" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="J137" s="24" t="s">
+      <c r="J137" s="4" t="s">
         <v>114</v>
       </c>
     </row>
@@ -6021,32 +6010,32 @@
       <c r="A138" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B138" s="23">
+      <c r="B138" s="8">
         <v>46287</v>
       </c>
-      <c r="C138" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D138" s="25">
+      <c r="C138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" s="5">
         <f t="shared" si="2"/>
         <v>0.92497184999999993</v>
       </c>
-      <c r="E138" s="26">
+      <c r="E138" s="7">
         <v>6.7</v>
       </c>
-      <c r="F138" s="24">
-        <v>5578</v>
-      </c>
-      <c r="G138" s="26">
+      <c r="F138" s="4">
+        <v>5578</v>
+      </c>
+      <c r="G138" s="7">
         <v>9</v>
       </c>
-      <c r="H138" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I138" s="26" t="s">
+      <c r="H138" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I138" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J138" s="24" t="s">
+      <c r="J138" s="4" t="s">
         <v>115</v>
       </c>
     </row>
@@ -6054,32 +6043,32 @@
       <c r="A139" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B139" s="23">
+      <c r="B139" s="8">
         <v>46287</v>
       </c>
-      <c r="C139" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D139" s="25">
+      <c r="C139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="5">
         <f t="shared" si="2"/>
         <v>0.71942254999999999</v>
       </c>
-      <c r="E139" s="26">
+      <c r="E139" s="7">
         <v>6.7</v>
       </c>
-      <c r="F139" s="24">
-        <v>5578</v>
-      </c>
-      <c r="G139" s="26">
+      <c r="F139" s="4">
+        <v>5578</v>
+      </c>
+      <c r="G139" s="7">
         <v>7</v>
       </c>
-      <c r="H139" s="26" t="s">
+      <c r="H139" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I139" s="26" t="s">
+      <c r="I139" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J139" s="24" t="s">
+      <c r="J139" s="4" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6087,32 +6076,32 @@
       <c r="A140" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B140" s="23">
+      <c r="B140" s="8">
         <v>46287</v>
       </c>
-      <c r="C140" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D140" s="25">
+      <c r="C140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140" s="5">
         <f t="shared" si="2"/>
         <v>1.2332958000000001</v>
       </c>
-      <c r="E140" s="26">
+      <c r="E140" s="7">
         <v>6.7</v>
       </c>
-      <c r="F140" s="24">
-        <v>5578</v>
-      </c>
-      <c r="G140" s="26">
-        <v>12</v>
-      </c>
-      <c r="H140" s="26" t="s">
+      <c r="F140" s="4">
+        <v>5578</v>
+      </c>
+      <c r="G140" s="7">
+        <v>12</v>
+      </c>
+      <c r="H140" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I140" s="26" t="s">
+      <c r="I140" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J140" s="24" t="s">
+      <c r="J140" s="4" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6120,32 +6109,32 @@
       <c r="A141" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B141" s="23">
+      <c r="B141" s="8">
         <v>46287</v>
       </c>
-      <c r="C141" s="24" t="s">
+      <c r="C141" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D141" s="25">
+      <c r="D141" s="5">
         <f t="shared" si="2"/>
         <v>0.51387324999999995</v>
       </c>
-      <c r="E141" s="26">
+      <c r="E141" s="7">
         <v>6.7</v>
       </c>
-      <c r="F141" s="24">
-        <v>5578</v>
-      </c>
-      <c r="G141" s="26">
+      <c r="F141" s="4">
+        <v>5578</v>
+      </c>
+      <c r="G141" s="7">
         <v>5</v>
       </c>
-      <c r="H141" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I141" s="26" t="s">
+      <c r="H141" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I141" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J141" s="24" t="s">
+      <c r="J141" s="4" t="s">
         <v>115</v>
       </c>
     </row>
@@ -6153,32 +6142,32 @@
       <c r="A142" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B142" s="27">
+      <c r="B142" s="18">
         <v>46287</v>
       </c>
-      <c r="C142" s="28" t="s">
+      <c r="C142" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D142" s="29">
+      <c r="D142" s="20">
         <f t="shared" si="2"/>
         <v>0.20554929999999999</v>
       </c>
-      <c r="E142" s="30">
+      <c r="E142" s="21">
         <v>6.7</v>
       </c>
-      <c r="F142" s="28">
-        <v>5578</v>
-      </c>
-      <c r="G142" s="30">
+      <c r="F142" s="19">
+        <v>5578</v>
+      </c>
+      <c r="G142" s="21">
         <v>2</v>
       </c>
-      <c r="H142" s="30" t="s">
+      <c r="H142" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="I142" s="30" t="s">
+      <c r="I142" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="J142" s="28" t="s">
+      <c r="J142" s="19" t="s">
         <v>117</v>
       </c>
     </row>
@@ -6186,32 +6175,32 @@
       <c r="A143" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B143" s="23">
+      <c r="B143" s="8">
         <v>46287</v>
       </c>
-      <c r="C143" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D143" s="25">
+      <c r="C143" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D143" s="5">
         <f t="shared" si="2"/>
         <v>1.6965487000000001</v>
       </c>
-      <c r="E143" s="26">
-        <v>15.8</v>
-      </c>
-      <c r="F143" s="24">
-        <v>5578</v>
-      </c>
-      <c r="G143" s="26">
+      <c r="E143" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="F143" s="4">
+        <v>5578</v>
+      </c>
+      <c r="G143" s="7">
         <v>7</v>
       </c>
-      <c r="H143" s="26" t="s">
+      <c r="H143" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="I143" s="26" t="s">
+      <c r="I143" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J143" s="24" t="s">
+      <c r="J143" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6219,32 +6208,32 @@
       <c r="A144" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B144" s="23">
+      <c r="B144" s="8">
         <v>46287</v>
       </c>
-      <c r="C144" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D144" s="25">
+      <c r="C144" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144" s="5">
         <f t="shared" si="2"/>
         <v>1.2118205000000002</v>
       </c>
-      <c r="E144" s="26">
-        <v>15.8</v>
-      </c>
-      <c r="F144" s="24">
-        <v>5578</v>
-      </c>
-      <c r="G144" s="26">
+      <c r="E144" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="F144" s="4">
+        <v>5578</v>
+      </c>
+      <c r="G144" s="7">
         <v>5</v>
       </c>
-      <c r="H144" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I144" s="26" t="s">
+      <c r="H144" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I144" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J144" s="24" t="s">
+      <c r="J144" s="4" t="s">
         <v>77</v>
       </c>
     </row>
@@ -6252,32 +6241,32 @@
       <c r="A145" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B145" s="23">
+      <c r="B145" s="8">
         <v>46287</v>
       </c>
-      <c r="C145" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D145" s="25">
+      <c r="C145" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D145" s="5">
         <f t="shared" si="2"/>
         <v>1.4541846</v>
       </c>
-      <c r="E145" s="26">
-        <v>15.8</v>
-      </c>
-      <c r="F145" s="24">
-        <v>5578</v>
-      </c>
-      <c r="G145" s="26">
+      <c r="E145" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="F145" s="4">
+        <v>5578</v>
+      </c>
+      <c r="G145" s="7">
         <v>6</v>
       </c>
-      <c r="H145" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I145" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="J145" s="24" t="s">
+      <c r="H145" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I145" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J145" s="4" t="s">
         <v>118</v>
       </c>
     </row>
@@ -6285,32 +6274,32 @@
       <c r="A146" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B146" s="23">
+      <c r="B146" s="8">
         <v>46287</v>
       </c>
-      <c r="C146" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D146" s="25">
+      <c r="C146" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146" s="5">
         <f t="shared" si="2"/>
         <v>1.2118205000000002</v>
       </c>
-      <c r="E146" s="26">
-        <v>15.8</v>
-      </c>
-      <c r="F146" s="24">
-        <v>5578</v>
-      </c>
-      <c r="G146" s="26">
+      <c r="E146" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="F146" s="4">
+        <v>5578</v>
+      </c>
+      <c r="G146" s="7">
         <v>5</v>
       </c>
-      <c r="H146" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I146" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="J146" s="24" t="s">
+      <c r="H146" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I146" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J146" s="4" t="s">
         <v>119</v>
       </c>
     </row>
@@ -6318,63 +6307,94 @@
       <c r="A147" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B147" s="23">
+      <c r="B147" s="8">
         <v>46287</v>
       </c>
-      <c r="C147" s="24" t="s">
+      <c r="C147" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D147" s="25">
+      <c r="D147" s="5">
         <f t="shared" si="2"/>
         <v>1.4541846</v>
       </c>
-      <c r="E147" s="26">
-        <v>15.8</v>
-      </c>
-      <c r="F147" s="24">
-        <v>5578</v>
-      </c>
-      <c r="G147" s="26">
+      <c r="E147" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="F147" s="4">
+        <v>5578</v>
+      </c>
+      <c r="G147" s="7">
         <v>6</v>
       </c>
-      <c r="H147" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I147" s="26" t="s">
+      <c r="H147" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I147" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J147" s="24"/>
+      <c r="J147" s="4"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B148" s="27">
+      <c r="B148" s="18">
         <v>46287</v>
       </c>
-      <c r="C148" s="28" t="s">
+      <c r="C148" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D148" s="29">
+      <c r="D148" s="20">
         <f t="shared" si="2"/>
         <v>0.48472820000000005</v>
       </c>
-      <c r="E148" s="30">
-        <v>15.8</v>
-      </c>
-      <c r="F148" s="28">
-        <v>5578</v>
-      </c>
-      <c r="G148" s="30">
+      <c r="E148" s="21">
+        <v>15.8</v>
+      </c>
+      <c r="F148" s="19">
+        <v>5578</v>
+      </c>
+      <c r="G148" s="21">
         <v>2</v>
       </c>
-      <c r="H148" s="30" t="s">
+      <c r="H148" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="I148" s="30" t="s">
+      <c r="I148" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="J148" s="28"/>
+      <c r="J148" s="19"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B149" s="24">
+        <v>46288</v>
+      </c>
+      <c r="C149" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D149" s="26">
+        <f t="shared" si="2"/>
+        <v>0.48472820000000005</v>
+      </c>
+      <c r="E149" s="27">
+        <v>15.8</v>
+      </c>
+      <c r="F149" s="25">
+        <v>5578</v>
+      </c>
+      <c r="G149" s="27">
+        <v>2</v>
+      </c>
+      <c r="H149" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="I149" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="J149" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
